--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table15.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table15.xlsx
@@ -373,7 +373,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -413,9 +413,6 @@
     <xf numFmtId="165" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -442,6 +439,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -456,12 +465,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -952,10 +955,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36">
+      <c r="B1" s="35">
         <v>5</v>
       </c>
     </row>
@@ -964,16 +967,16 @@
       <c r="B2" s="7"/>
     </row>
     <row r="3" spans="1:21" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="34" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="8"/>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="36" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="37" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
@@ -981,7 +984,7 @@
       </c>
     </row>
     <row r="5" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="37" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
@@ -989,7 +992,7 @@
       </c>
     </row>
     <row r="6" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="37" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -997,7 +1000,7 @@
       </c>
     </row>
     <row r="7" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="37" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
@@ -1005,7 +1008,7 @@
       </c>
     </row>
     <row r="8" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="37" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -1013,7 +1016,7 @@
       </c>
     </row>
     <row r="9" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="37" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -1025,55 +1028,55 @@
       <c r="B10" s="12"/>
     </row>
     <row r="11" spans="1:21" ht="13" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="40" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:21" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="38" t="s">
+      <c r="C12" s="43"/>
+      <c r="D12" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="39" t="s">
+      <c r="E12" s="41"/>
+      <c r="F12" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="40"/>
-      <c r="H12" s="38" t="s">
+      <c r="G12" s="43"/>
+      <c r="H12" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="I12" s="38"/>
-      <c r="J12" s="39" t="s">
+      <c r="I12" s="41"/>
+      <c r="J12" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="40"/>
-      <c r="L12" s="38" t="s">
+      <c r="K12" s="43"/>
+      <c r="L12" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="M12" s="38"/>
-      <c r="N12" s="39" t="s">
+      <c r="M12" s="41"/>
+      <c r="N12" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="O12" s="40"/>
-      <c r="P12" s="38" t="s">
+      <c r="O12" s="43"/>
+      <c r="P12" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="41" t="s">
+      <c r="Q12" s="41"/>
+      <c r="R12" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="S12" s="42"/>
-      <c r="T12" s="39" t="s">
+      <c r="S12" s="45"/>
+      <c r="T12" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="U12" s="40"/>
+      <c r="U12" s="43"/>
     </row>
     <row r="13" spans="1:21" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="38" t="s">
         <v>26</v>
       </c>
       <c r="B13" s="14">
@@ -1156,49 +1159,49 @@
       <c r="F14" s="17">
         <v>77.919179949043098</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="23">
         <v>91.828233102714194</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="24">
         <v>35.687573964496998</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="24">
         <v>39.970089939343197</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="30">
         <v>54.559048490393401</v>
       </c>
-      <c r="K14" s="24">
+      <c r="K14" s="23">
         <v>45.0457671495898</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="24">
         <v>46.347156802512103</v>
       </c>
-      <c r="M14" s="25">
+      <c r="M14" s="24">
         <v>47.6965939729645</v>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="30">
         <v>33.7429335024461</v>
       </c>
-      <c r="O14" s="24">
+      <c r="O14" s="23">
         <v>36.719919191919203</v>
       </c>
-      <c r="P14" s="25">
+      <c r="P14" s="24">
         <v>36.897573778887399</v>
       </c>
-      <c r="Q14" s="25">
+      <c r="Q14" s="24">
         <v>55.558374264586803</v>
       </c>
-      <c r="R14" s="31">
+      <c r="R14" s="30">
         <v>31.261221786314799</v>
       </c>
-      <c r="S14" s="24">
+      <c r="S14" s="23">
         <v>29.7563712882862</v>
       </c>
-      <c r="T14" s="31">
+      <c r="T14" s="30">
         <v>46.679106797457898</v>
       </c>
-      <c r="U14" s="24">
+      <c r="U14" s="23">
         <v>48.448622424581799</v>
       </c>
     </row>
@@ -1215,55 +1218,55 @@
       <c r="D15" s="19">
         <v>163.57018813313999</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="25" t="s">
         <v>29</v>
       </c>
       <c r="F15" s="17">
         <v>88.415384615384596</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="G15" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="24">
         <v>79.6527777777778</v>
       </c>
-      <c r="I15" s="32" t="s">
+      <c r="I15" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="31">
+      <c r="J15" s="30">
         <v>79.598820058997006</v>
       </c>
-      <c r="K15" s="27" t="s">
+      <c r="K15" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="L15" s="25">
+      <c r="L15" s="24">
         <v>157.325814536341</v>
       </c>
-      <c r="M15" s="32" t="s">
+      <c r="M15" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="N15" s="31">
+      <c r="N15" s="30">
         <v>62.964125560538101</v>
       </c>
-      <c r="O15" s="27" t="s">
+      <c r="O15" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="P15" s="25">
+      <c r="P15" s="24">
         <v>57.324455205811098</v>
       </c>
-      <c r="Q15" s="32" t="s">
+      <c r="Q15" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R15" s="31">
+      <c r="R15" s="30">
         <v>80.199211045364905</v>
       </c>
-      <c r="S15" s="27" t="s">
+      <c r="S15" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="T15" s="31">
+      <c r="T15" s="30">
         <v>107.341908531223</v>
       </c>
-      <c r="U15" s="27" t="s">
+      <c r="U15" s="26" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1274,84 +1277,84 @@
       <c r="D16" s="19"/>
       <c r="E16" s="19"/>
       <c r="F16" s="17"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="31"/>
-      <c r="U16" s="24"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="23"/>
     </row>
     <row r="17" spans="1:21" s="3" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="21">
         <v>48.7290663352493</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="22">
         <v>43.942522050983797</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>34.853917762785997</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="21">
         <v>36.602553238019702</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="27">
         <v>77.979469203805706</v>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="28">
         <v>91.828233102714194</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="29">
         <v>36.303189420458999</v>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="29">
         <v>39.970089939343197</v>
       </c>
-      <c r="J17" s="33">
+      <c r="J17" s="32">
         <v>55.165303717458798</v>
       </c>
-      <c r="K17" s="29">
+      <c r="K17" s="28">
         <v>45.0457671495898</v>
       </c>
-      <c r="L17" s="30">
+      <c r="L17" s="29">
         <v>47.838232818129804</v>
       </c>
-      <c r="M17" s="30">
+      <c r="M17" s="29">
         <v>47.6965939729645</v>
       </c>
-      <c r="N17" s="33">
+      <c r="N17" s="32">
         <v>34.321596661042499</v>
       </c>
-      <c r="O17" s="29">
+      <c r="O17" s="28">
         <v>36.719919191919203</v>
       </c>
-      <c r="P17" s="30">
+      <c r="P17" s="29">
         <v>37.423724585256302</v>
       </c>
-      <c r="Q17" s="30">
+      <c r="Q17" s="29">
         <v>55.558374264586803</v>
       </c>
-      <c r="R17" s="33">
+      <c r="R17" s="32">
         <v>32.493543260156898</v>
       </c>
-      <c r="S17" s="29">
+      <c r="S17" s="28">
         <v>29.7563712882862</v>
       </c>
-      <c r="T17" s="33">
+      <c r="T17" s="32">
         <v>47.847339137209701</v>
       </c>
-      <c r="U17" s="29">
+      <c r="U17" s="28">
         <v>48.448622424581799</v>
       </c>
     </row>
